--- a/questionari/risposte/Subject Information (Responses).xlsx
+++ b/questionari/risposte/Subject Information (Responses).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>Timestamp</t>
   </si>
@@ -26,12 +26,48 @@
   </si>
   <si>
     <t>Have you any experience with interfaces and/or videogames?</t>
+  </si>
+  <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>S002</t>
+  </si>
+  <si>
+    <t>S003</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>S004</t>
+  </si>
+  <si>
+    <t>S005</t>
+  </si>
+  <si>
+    <t>S006</t>
+  </si>
+  <si>
+    <t>S007</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="10.0"/>
@@ -59,12 +95,24 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -145,20 +193,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:E1" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E8" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="5">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
+    <tableColumn name="Timestamp" id="1"/>
+    <tableColumn name="ID " id="2"/>
+    <tableColumn name="Gender" id="3"/>
+    <tableColumn name="Age" id="4"/>
+    <tableColumn name="Have you any experience with interfaces and/or videogames?" id="5"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
-    </ext>
-  </extLst>
 </table>
 </file>
 
@@ -385,6 +428,125 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="2">
+        <v>46294.761391493055</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="4">
+        <v>46295.38550712963</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5">
+        <v>26.0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="4">
+        <v>46295.45452712963</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5">
+        <v>25.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="4">
+        <v>46295.50326462963</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5">
+        <v>27.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="4">
+        <v>46295.61193802083</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5">
+        <v>25.0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="4">
+        <v>46295.67338824074</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="5">
+        <v>26.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="4">
+        <v>46295.72063969907</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5">
+        <v>28.0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
   <tableParts count="1">

--- a/questionari/risposte/Subject Information (Responses).xlsx
+++ b/questionari/risposte/Subject Information (Responses).xlsx
@@ -1,89 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form Responses 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID </t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Have you any experience with interfaces and/or videogames?</t>
-  </si>
-  <si>
-    <t>S001</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>S002</t>
-  </si>
-  <si>
-    <t>S003</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>S004</t>
-  </si>
-  <si>
-    <t>S005</t>
-  </si>
-  <si>
-    <t>S006</t>
-  </si>
-  <si>
-    <t>S007</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -93,36 +40,37 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
       <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill/>
       </fill>
       <border/>
     </dxf>
@@ -173,35 +121,95 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Form Responses 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Form Responses 1-style" pivot="0" count="4">
+      <tableStyleElement type="headerRow" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E8" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:E7" headerRowCount="1">
   <tableColumns count="5">
-    <tableColumn name="Timestamp" id="1"/>
-    <tableColumn name="ID " id="2"/>
-    <tableColumn name="Gender" id="3"/>
-    <tableColumn name="Age" id="4"/>
-    <tableColumn name="Have you any experience with interfaces and/or videogames?" id="5"/>
+    <tableColumn id="1" name="Timestamp"/>
+    <tableColumn id="2" name="ID "/>
+    <tableColumn id="3" name="Gender"/>
+    <tableColumn id="4" name="Age"/>
+    <tableColumn id="5" name="Have you any experience with interfaces and/or videogames?"/>
   </tableColumns>
-  <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form Responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -400,157 +408,189 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="18.88"/>
-    <col customWidth="1" min="5" max="5" width="37.63"/>
-    <col customWidth="1" min="6" max="11" width="18.88"/>
+    <col width="18.88" customWidth="1" style="6" min="1" max="4"/>
+    <col width="37.63" customWidth="1" style="6" min="5" max="5"/>
+    <col width="18.88" customWidth="1" style="6" min="6" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="2">
-        <v>46294.761391493055</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="4">
-        <v>46295.38550712963</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="5">
-        <v>26.0</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="4">
+    <row r="1" ht="22.5" customHeight="1" s="6">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID </t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Have you any experience with interfaces and/or videogames?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" s="6">
+      <c r="A2" s="4" t="n">
+        <v>46294.76139149306</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" s="6">
+      <c r="A3" s="4" t="n">
         <v>46295.45452712963</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5">
-        <v>25.0</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="4">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" s="6">
+      <c r="A4" s="4" t="n">
         <v>46295.50326462963</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="5">
-        <v>27.0</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1" s="6">
+      <c r="A5" s="4" t="n">
         <v>46295.61193802083</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="5">
-        <v>25.0</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="4">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1" s="6">
+      <c r="A6" s="4" t="n">
         <v>46295.67338824074</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="5">
-        <v>26.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="4">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1" s="6">
+      <c r="A7" s="4" t="n">
         <v>46295.72063969907</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5">
-        <v>28.0</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1" s="6"/>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/questionari/risposte/Subject Information (Responses).xlsx
+++ b/questionari/risposte/Subject Information (Responses).xlsx
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:E7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:E12" headerRowCount="1">
   <tableColumns count="5">
     <tableColumn id="1" name="Timestamp"/>
     <tableColumn id="2" name="ID "/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.88" customWidth="1" style="6" min="1" max="4"/>
@@ -586,7 +586,121 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1" s="6"/>
+    <row r="8" ht="22.5" customHeight="1" s="6">
+      <c r="A8" s="4" t="n">
+        <v>46296.4331753588</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>S007</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1" s="6">
+      <c r="A9" s="4" t="n">
+        <v>46296.49567744213</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" s="6">
+      <c r="A10" s="4" t="n">
+        <v>46296.58521494213</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>S009</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1" s="6">
+      <c r="A11" s="4" t="n">
+        <v>46296.6406594213</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1" s="6">
+      <c r="A12" s="4" t="n">
+        <v>46296.68956917824</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/questionari/risposte/Subject Information (Responses).xlsx
+++ b/questionari/risposte/Subject Information (Responses).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.88" customWidth="1" style="6" min="1" max="4"/>
@@ -588,7 +588,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1" s="6">
       <c r="A8" s="4" t="n">
-        <v>46296.4331753588</v>
+        <v>46296.49567744213</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -597,11 +597,11 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
     </row>
     <row r="9" ht="22.5" customHeight="1" s="6">
       <c r="A9" s="4" t="n">
-        <v>46296.49567744213</v>
+        <v>46296.58521494213</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -620,11 +620,11 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="10" ht="22.5" customHeight="1" s="6">
       <c r="A10" s="4" t="n">
-        <v>46296.58521494213</v>
+        <v>46296.6406594213</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
     </row>
     <row r="11" ht="22.5" customHeight="1" s="6">
       <c r="A11" s="4" t="n">
-        <v>46296.6406594213</v>
+        <v>46296.68956917824</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -678,29 +678,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1" s="6">
-      <c r="A12" s="4" t="n">
-        <v>46296.68956917824</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>S011</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
+    <row r="12" ht="22.5" customHeight="1" s="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
